--- a/example/schema_example.xlsx
+++ b/example/schema_example.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="71">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -49,17 +49,13 @@
     <t xml:space="preserve">min_max</t>
   </si>
   <si>
-    <t xml:space="preserve">in English, no abbreviation. This is probably the only description of the parameters that the user will read! Be very clear and explicit, otherwise put a redmine reference or fill in ADD reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Off-line "general case" default value. For the real use the point after decimal.
-No default indicates that the parameter is required or no</t>
+    <t xml:space="preserve">as example</t>
   </si>
   <si>
     <t xml:space="preserve">if there is no unit, keep empty</t>
   </si>
   <si>
-    <t xml:space="preserve">Available type "boolean", "number", "string","integer" or « enum ». Can be array with keyword « array » at first position. Comment : no merge of type for array</t>
+    <t xml:space="preserve">Available type : number, string, integer , enum , pdf,  jpg, csv and array. For array with keyword « array » at first position. Comment : no merge of type for array</t>
   </si>
   <si>
     <t xml:space="preserve">Indicate list of keywords allowed comma separated</t>
@@ -344,11 +340,35 @@
       <protection locked="false" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -357,6 +377,18 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -366,7 +398,23 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -374,11 +422,31 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -387,6 +455,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -411,344 +483,340 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:O14"/>
-  <sheetFormatPr defaultColWidth="13.5078125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="22.66796875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="32.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1018" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="33.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="25.98"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="22.64"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="22.64"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="7" style="4" width="22.64"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="8" style="5" width="22.64"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="22.64"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4" t="s">
+    <row r="2" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="13"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="I2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="K2" s="13"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
+      <c r="B3" s="21"/>
+      <c r="C3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="16"/>
+      <c r="F3" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8" t="s">
+      <c r="G3" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="H3" s="23"/>
+      <c r="I3" s="16"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="B4" s="21"/>
+      <c r="C4" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8" t="s">
+      <c r="G4" s="22"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="16"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-    </row>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="B5" s="19"/>
+      <c r="C5" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="G5" s="26"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9" t="s">
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="B6" s="19"/>
+      <c r="C6" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="9" t="s">
+      <c r="E6" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="9" t="s">
+      <c r="G6" s="26"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+    </row>
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-    </row>
-    <row r="7" customFormat="false" ht="44.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+      <c r="B7" s="19"/>
+      <c r="C7" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9" t="s">
+      <c r="G7" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="H7" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="I7" s="25"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19"/>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="I7" s="9"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="B8" s="19"/>
+      <c r="C8" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="25"/>
+      <c r="F8" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9" t="s">
+      <c r="G8" s="26"/>
+      <c r="H8" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9" t="s">
+      <c r="I8" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-    </row>
-    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="C9" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="D9" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="E9" s="29"/>
+      <c r="F9" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="6" t="s">
+      <c r="H9" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="I9" s="25"/>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I9" s="6"/>
-    </row>
-    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="C10" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="D10" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="E10" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="F10" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="G10" s="26"/>
+      <c r="H10" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="9" t="s">
+      <c r="I10" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="I10" s="6" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="C11" s="28"/>
+      <c r="D11" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="0" t="s">
+      <c r="E11" s="29"/>
+      <c r="F11" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" s="26"/>
+      <c r="H11" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6" t="s">
+      <c r="I11" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="I11" s="6" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="C12" s="0" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="D12" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="F12" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="0" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="C13" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="D13" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="F13" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="0" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="C14" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="D14" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="F14" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="F14" s="0" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
